--- a/STUDENT_PERFORMANCE_AND_ATTENDANCE_TRACKER.xlsx
+++ b/STUDENT_PERFORMANCE_AND_ATTENDANCE_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B62D24AB-4A8D-4E44-A060-8223DA1D014C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D50BF8D-CCC0-4BB4-A915-A643634E2E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{305D8DE4-2A48-4DF2-A8B8-C5EA1F24A9C2}"/>
   </bookViews>
@@ -426,9 +426,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -494,269 +491,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00CC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -778,22 +521,37 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00CC00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1146,767 +904,767 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="14">
-        <v>12</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="C3" s="13">
+        <v>12</v>
+      </c>
+      <c r="D3" s="11">
         <v>80</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>78</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>84</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <f>SUM(D3:F3)</f>
         <v>242</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <f>AVERAGE(D3:F3)</f>
         <v>80.666666666666671</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <f ca="1">RANDBETWEEN(60,100)</f>
-        <v>93</v>
-      </c>
-      <c r="J3" s="13" t="str">
+        <v>74</v>
+      </c>
+      <c r="J3" s="12" t="str">
         <f>IF(H3&gt;=80,"Excellent",IF(H3&gt;=60,"Good",IF(H3&gt;=40,"Average","Needs Improvement")))</f>
         <v>Excellent</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="14">
-        <v>12</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="B4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="13">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11">
         <v>75</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>59</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>26</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <f t="shared" ref="G4:G22" si="0">SUM(D4:F4)</f>
         <v>160</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f t="shared" ref="H4:H22" si="1">AVERAGE(D4:F4)</f>
         <v>53.333333333333336</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <f t="shared" ref="I4:I22" ca="1" si="2">RANDBETWEEN(60,100)</f>
-        <v>63</v>
-      </c>
-      <c r="J4" s="13" t="str">
+        <v>97</v>
+      </c>
+      <c r="J4" s="12" t="str">
         <f t="shared" ref="J4:J22" si="3">IF(H4&gt;=80,"Excellent",IF(H4&gt;=60,"Good",IF(H4&gt;=40,"Average","Needs Improvement")))</f>
         <v>Average</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="14">
-        <v>12</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C5" s="13">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11">
         <v>54</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>56</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>21</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f t="shared" si="1"/>
         <v>43.666666666666664</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="J5" s="13" t="str">
+        <v>89</v>
+      </c>
+      <c r="J5" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Average</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="14">
-        <v>12</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="13">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11">
         <v>87</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>48</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>26</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f t="shared" si="1"/>
         <v>53.666666666666664</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J6" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="13">
+        <v>12</v>
+      </c>
+      <c r="D7" s="11">
+        <v>59</v>
+      </c>
+      <c r="E7" s="11">
+        <v>89</v>
+      </c>
+      <c r="F7" s="11">
+        <v>84</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" si="0"/>
+        <v>232</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="1"/>
+        <v>77.333333333333329</v>
+      </c>
+      <c r="I7" s="11">
         <f t="shared" ca="1" si="2"/>
         <v>75</v>
       </c>
-      <c r="J6" s="13" t="str">
+      <c r="J7" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="13">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11">
+        <v>87</v>
+      </c>
+      <c r="E8" s="11">
+        <v>59</v>
+      </c>
+      <c r="F8" s="11">
+        <v>64</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="H8" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="J8" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="13">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11">
+        <v>53</v>
+      </c>
+      <c r="E9" s="11">
+        <v>58</v>
+      </c>
+      <c r="F9" s="11">
+        <v>66</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="H9" s="12">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="J9" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Average</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="14">
-        <v>12</v>
-      </c>
-      <c r="D7" s="12">
-        <v>59</v>
-      </c>
-      <c r="E7" s="12">
-        <v>89</v>
-      </c>
-      <c r="F7" s="12">
-        <v>84</v>
-      </c>
-      <c r="G7" s="12">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13">
+        <v>12</v>
+      </c>
+      <c r="D10" s="11">
+        <v>87</v>
+      </c>
+      <c r="E10" s="11">
+        <v>49</v>
+      </c>
+      <c r="F10" s="11">
+        <v>97</v>
+      </c>
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
-        <v>232</v>
-      </c>
-      <c r="H7" s="13">
+        <v>233</v>
+      </c>
+      <c r="H10" s="12">
         <f t="shared" si="1"/>
-        <v>77.333333333333329</v>
-      </c>
-      <c r="I7" s="12">
+        <v>77.666666666666671</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J10" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="13">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11">
+        <v>54</v>
+      </c>
+      <c r="E11" s="11">
+        <v>26</v>
+      </c>
+      <c r="F11" s="11">
+        <v>54</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="1"/>
+        <v>44.666666666666664</v>
+      </c>
+      <c r="I11" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="J11" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13">
+        <v>12</v>
+      </c>
+      <c r="D12" s="11">
+        <v>26</v>
+      </c>
+      <c r="E12" s="11">
+        <v>98</v>
+      </c>
+      <c r="F12" s="11">
+        <v>21</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="0"/>
+        <v>145</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="1"/>
+        <v>48.333333333333336</v>
+      </c>
+      <c r="I12" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="J12" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="13">
+        <v>12</v>
+      </c>
+      <c r="D13" s="11">
+        <v>14</v>
+      </c>
+      <c r="E13" s="11">
+        <v>54</v>
+      </c>
+      <c r="F13" s="11">
+        <v>98</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+      <c r="H13" s="12">
+        <f t="shared" si="1"/>
+        <v>55.333333333333336</v>
+      </c>
+      <c r="I13" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="J13" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="13">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11">
+        <v>86</v>
+      </c>
+      <c r="E14" s="11">
+        <v>78</v>
+      </c>
+      <c r="F14" s="11">
+        <v>65</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="0"/>
+        <v>229</v>
+      </c>
+      <c r="H14" s="12">
+        <f t="shared" si="1"/>
+        <v>76.333333333333329</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="J14" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="13">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>25</v>
+      </c>
+      <c r="E15" s="11">
+        <v>21</v>
+      </c>
+      <c r="F15" s="11">
+        <v>64</v>
+      </c>
+      <c r="G15" s="16">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="1"/>
+        <v>36.666666666666664</v>
+      </c>
+      <c r="I15" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>97</v>
       </c>
-      <c r="J7" s="13" t="str">
+      <c r="J15" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="13">
+        <v>12</v>
+      </c>
+      <c r="D16" s="11">
+        <v>87</v>
+      </c>
+      <c r="E16" s="11">
+        <v>98</v>
+      </c>
+      <c r="F16" s="14">
+        <v>24</v>
+      </c>
+      <c r="G16" s="20">
+        <f t="shared" si="0"/>
+        <v>209</v>
+      </c>
+      <c r="H16" s="21">
+        <f t="shared" si="1"/>
+        <v>69.666666666666671</v>
+      </c>
+      <c r="I16" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="J16" s="15" t="str">
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>6</v>
-      </c>
-      <c r="B8" s="13" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="13">
+        <v>12</v>
+      </c>
+      <c r="D17" s="11">
+        <v>59</v>
+      </c>
+      <c r="E17" s="11">
+        <v>32</v>
+      </c>
+      <c r="F17" s="14">
+        <v>65</v>
+      </c>
+      <c r="G17" s="23">
+        <f t="shared" si="0"/>
+        <v>156</v>
+      </c>
+      <c r="H17" s="12">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="I17" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="J17" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
         <v>16</v>
       </c>
-      <c r="C8" s="14">
-        <v>12</v>
-      </c>
-      <c r="D8" s="12">
-        <v>87</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="B18" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="13">
+        <v>12</v>
+      </c>
+      <c r="D18" s="11">
+        <v>58</v>
+      </c>
+      <c r="E18" s="11">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14">
+        <v>98</v>
+      </c>
+      <c r="G18" s="23">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="H18" s="12">
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="F8" s="12">
-        <v>64</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="I18" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="J18" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="13">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11">
+        <v>57</v>
+      </c>
+      <c r="E19" s="11">
+        <v>56</v>
+      </c>
+      <c r="F19" s="14">
+        <v>54</v>
+      </c>
+      <c r="G19" s="23">
         <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-      <c r="H8" s="13">
+        <v>167</v>
+      </c>
+      <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="I8" s="12">
+        <v>55.666666666666664</v>
+      </c>
+      <c r="I19" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>81</v>
-      </c>
-      <c r="J8" s="13" t="str">
+        <v>98</v>
+      </c>
+      <c r="J19" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>Average</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="13">
+        <v>12</v>
+      </c>
+      <c r="D20" s="11">
+        <v>98</v>
+      </c>
+      <c r="E20" s="11">
+        <v>65</v>
+      </c>
+      <c r="F20" s="14">
+        <v>26</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="0"/>
+        <v>189</v>
+      </c>
+      <c r="H20" s="26">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="I20" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="J20" s="15" t="str">
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>7</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="14">
-        <v>12</v>
-      </c>
-      <c r="D9" s="12">
-        <v>53</v>
-      </c>
-      <c r="E9" s="12">
-        <v>58</v>
-      </c>
-      <c r="F9" s="12">
-        <v>66</v>
-      </c>
-      <c r="G9" s="12">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="13">
+        <v>12</v>
+      </c>
+      <c r="D21" s="11">
+        <v>56</v>
+      </c>
+      <c r="E21" s="11">
+        <v>51</v>
+      </c>
+      <c r="F21" s="11">
+        <v>87</v>
+      </c>
+      <c r="G21" s="18">
         <f t="shared" si="0"/>
-        <v>177</v>
-      </c>
-      <c r="H9" s="13">
+        <v>194</v>
+      </c>
+      <c r="H21" s="19">
         <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="I9" s="12">
+        <v>64.666666666666671</v>
+      </c>
+      <c r="I21" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
-      </c>
-      <c r="J9" s="13" t="str">
+        <v>79</v>
+      </c>
+      <c r="J21" s="12" t="str">
         <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>8</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="14">
-        <v>12</v>
-      </c>
-      <c r="D10" s="12">
-        <v>87</v>
-      </c>
-      <c r="E10" s="12">
-        <v>49</v>
-      </c>
-      <c r="F10" s="12">
-        <v>97</v>
-      </c>
-      <c r="G10" s="12">
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="13">
+        <v>12</v>
+      </c>
+      <c r="D22" s="11">
+        <v>22</v>
+      </c>
+      <c r="E22" s="11">
+        <v>23</v>
+      </c>
+      <c r="F22" s="11">
+        <v>98</v>
+      </c>
+      <c r="G22" s="11">
         <f t="shared" si="0"/>
-        <v>233</v>
-      </c>
-      <c r="H10" s="13">
+        <v>143</v>
+      </c>
+      <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>77.666666666666671</v>
-      </c>
-      <c r="I10" s="12">
+        <v>47.666666666666664</v>
+      </c>
+      <c r="I22" s="11">
         <f t="shared" ca="1" si="2"/>
         <v>71</v>
       </c>
-      <c r="J10" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Good</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="14">
-        <v>12</v>
-      </c>
-      <c r="D11" s="12">
-        <v>54</v>
-      </c>
-      <c r="E11" s="12">
-        <v>26</v>
-      </c>
-      <c r="F11" s="12">
-        <v>54</v>
-      </c>
-      <c r="G11" s="12">
-        <f t="shared" si="0"/>
-        <v>134</v>
-      </c>
-      <c r="H11" s="13">
-        <f t="shared" si="1"/>
-        <v>44.666666666666664</v>
-      </c>
-      <c r="I11" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="J11" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14">
-        <v>12</v>
-      </c>
-      <c r="D12" s="12">
-        <v>26</v>
-      </c>
-      <c r="E12" s="12">
-        <v>98</v>
-      </c>
-      <c r="F12" s="12">
-        <v>21</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="0"/>
-        <v>145</v>
-      </c>
-      <c r="H12" s="13">
-        <f t="shared" si="1"/>
-        <v>48.333333333333336</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="J12" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
-        <v>11</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="14">
-        <v>12</v>
-      </c>
-      <c r="D13" s="12">
-        <v>14</v>
-      </c>
-      <c r="E13" s="12">
-        <v>54</v>
-      </c>
-      <c r="F13" s="12">
-        <v>98</v>
-      </c>
-      <c r="G13" s="12">
-        <f t="shared" si="0"/>
-        <v>166</v>
-      </c>
-      <c r="H13" s="13">
-        <f t="shared" si="1"/>
-        <v>55.333333333333336</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="J13" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
-        <v>12</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="14">
-        <v>12</v>
-      </c>
-      <c r="D14" s="12">
-        <v>86</v>
-      </c>
-      <c r="E14" s="12">
-        <v>78</v>
-      </c>
-      <c r="F14" s="12">
-        <v>65</v>
-      </c>
-      <c r="G14" s="12">
-        <f t="shared" si="0"/>
-        <v>229</v>
-      </c>
-      <c r="H14" s="13">
-        <f t="shared" si="1"/>
-        <v>76.333333333333329</v>
-      </c>
-      <c r="I14" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="J14" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Good</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
-        <v>13</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="14">
-        <v>12</v>
-      </c>
-      <c r="D15" s="12">
-        <v>25</v>
-      </c>
-      <c r="E15" s="12">
-        <v>21</v>
-      </c>
-      <c r="F15" s="12">
-        <v>64</v>
-      </c>
-      <c r="G15" s="17">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="H15" s="18">
-        <f t="shared" si="1"/>
-        <v>36.666666666666664</v>
-      </c>
-      <c r="I15" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="J15" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Needs Improvement</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
-        <v>14</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="14">
-        <v>12</v>
-      </c>
-      <c r="D16" s="12">
-        <v>87</v>
-      </c>
-      <c r="E16" s="12">
-        <v>98</v>
-      </c>
-      <c r="F16" s="15">
-        <v>24</v>
-      </c>
-      <c r="G16" s="21">
-        <f t="shared" si="0"/>
-        <v>209</v>
-      </c>
-      <c r="H16" s="22">
-        <f t="shared" si="1"/>
-        <v>69.666666666666671</v>
-      </c>
-      <c r="I16" s="23">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="J16" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>Good</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
-        <v>15</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="14">
-        <v>12</v>
-      </c>
-      <c r="D17" s="12">
-        <v>59</v>
-      </c>
-      <c r="E17" s="12">
-        <v>32</v>
-      </c>
-      <c r="F17" s="15">
-        <v>65</v>
-      </c>
-      <c r="G17" s="24">
-        <f t="shared" si="0"/>
-        <v>156</v>
-      </c>
-      <c r="H17" s="13">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="I17" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>82</v>
-      </c>
-      <c r="J17" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
-        <v>16</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="14">
-        <v>12</v>
-      </c>
-      <c r="D18" s="12">
-        <v>58</v>
-      </c>
-      <c r="E18" s="12">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>98</v>
-      </c>
-      <c r="G18" s="24">
-        <f t="shared" si="0"/>
-        <v>177</v>
-      </c>
-      <c r="H18" s="13">
-        <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="I18" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>86</v>
-      </c>
-      <c r="J18" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
-        <v>17</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="14">
-        <v>12</v>
-      </c>
-      <c r="D19" s="12">
-        <v>57</v>
-      </c>
-      <c r="E19" s="12">
-        <v>56</v>
-      </c>
-      <c r="F19" s="15">
-        <v>54</v>
-      </c>
-      <c r="G19" s="24">
-        <f t="shared" si="0"/>
-        <v>167</v>
-      </c>
-      <c r="H19" s="13">
-        <f t="shared" si="1"/>
-        <v>55.666666666666664</v>
-      </c>
-      <c r="I19" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="J19" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>Average</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
-        <v>18</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="14">
-        <v>12</v>
-      </c>
-      <c r="D20" s="12">
-        <v>98</v>
-      </c>
-      <c r="E20" s="12">
-        <v>65</v>
-      </c>
-      <c r="F20" s="15">
-        <v>26</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>189</v>
-      </c>
-      <c r="H20" s="27">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="I20" s="28">
-        <f t="shared" ca="1" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="J20" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>Good</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
-        <v>19</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="14">
-        <v>12</v>
-      </c>
-      <c r="D21" s="12">
-        <v>56</v>
-      </c>
-      <c r="E21" s="12">
-        <v>51</v>
-      </c>
-      <c r="F21" s="12">
-        <v>87</v>
-      </c>
-      <c r="G21" s="19">
-        <f t="shared" si="0"/>
-        <v>194</v>
-      </c>
-      <c r="H21" s="20">
-        <f t="shared" si="1"/>
-        <v>64.666666666666671</v>
-      </c>
-      <c r="I21" s="19">
-        <f t="shared" ca="1" si="2"/>
-        <v>86</v>
-      </c>
-      <c r="J21" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>Good</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
-        <v>20</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="14">
-        <v>12</v>
-      </c>
-      <c r="D22" s="12">
-        <v>22</v>
-      </c>
-      <c r="E22" s="12">
-        <v>23</v>
-      </c>
-      <c r="F22" s="12">
-        <v>98</v>
-      </c>
-      <c r="G22" s="12">
-        <f t="shared" si="0"/>
-        <v>143</v>
-      </c>
-      <c r="H22" s="13">
-        <f t="shared" si="1"/>
-        <v>47.666666666666664</v>
-      </c>
-      <c r="I22" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="J22" s="13" t="str">
+      <c r="J22" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Average</v>
       </c>
@@ -1915,31 +1673,28 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:J22">
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="Excellent">
+  <conditionalFormatting sqref="J3">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Excellent">
       <formula>NOT(ISERROR(SEARCH("Excellent",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="Good">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J22">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Good">
       <formula>NOT(ISERROR(SEARCH("Good",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="Average">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Needs Improvement">
+      <formula>NOT(ISERROR(SEARCH("Needs Improvement",J3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Eccellent">
+      <formula>NOT(ISERROR(SEARCH("Eccellent",J3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Average">
       <formula>NOT(ISERROR(SEARCH("Average",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="Eccellent">
-      <formula>NOT(ISERROR(SEARCH("Eccellent",J3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Needs Improvement">
-      <formula>NOT(ISERROR(SEARCH("Needs Improvement",J3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Good">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Good">
       <formula>NOT(ISERROR(SEARCH("Good",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",J3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Excellent">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Excellent">
       <formula>NOT(ISERROR(SEARCH("Excellent",J3)))</formula>
     </cfRule>
   </conditionalFormatting>
